--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -1136,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2100"/>
+  <dimension ref="A1:D2101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30545,6 +30545,20 @@
       </c>
       <c r="D2100" t="n">
         <v>196413.2</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>132706.3</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>65271.7</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>197978</v>
       </c>
     </row>
   </sheetData>
@@ -31534,7 +31548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2100"/>
+  <dimension ref="A1:E2101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67244,6 +67258,23 @@
         <v>388.4</v>
       </c>
       <c r="E2100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>55456.6</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>5802.7</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="E2101" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -31,8 +31,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -72,12 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1080,7 +1081,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1095,7 +1095,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1110,7 +1109,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -67432,7 +67430,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -67458,7 +67456,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -67484,7 +67482,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -67510,7 +67508,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -67536,7 +67534,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -67562,7 +67560,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -67588,7 +67586,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -67614,7 +67612,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -67640,7 +67638,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -67666,7 +67664,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -67692,7 +67690,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -67718,7 +67716,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -67744,7 +67742,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -67770,7 +67768,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -67796,7 +67794,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -67822,7 +67820,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -67848,7 +67846,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -67874,7 +67872,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -67900,7 +67898,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -67926,7 +67924,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -67952,7 +67950,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -67978,7 +67976,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -68004,7 +68002,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -68030,7 +68028,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -68056,7 +68054,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -68082,7 +68080,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -68108,7 +68106,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -68134,7 +68132,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -68160,7 +68158,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -68186,7 +68184,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -68212,7 +68210,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -68238,7 +68236,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -68264,7 +68262,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -68290,7 +68288,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -68316,7 +68314,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -68342,7 +68340,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -68368,7 +68366,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -68394,7 +68392,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -68420,7 +68418,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -68446,7 +68444,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -68472,7 +68470,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -68498,7 +68496,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -68524,7 +68522,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -68550,7 +68548,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -68576,7 +68574,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -68602,7 +68600,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -68628,7 +68626,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -68654,7 +68652,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -68680,7 +68678,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -68706,7 +68704,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -68732,7 +68730,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -68758,7 +68756,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -68784,7 +68782,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -68810,7 +68808,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -68836,7 +68834,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -68862,7 +68860,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -68888,7 +68886,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -68914,7 +68912,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -68940,7 +68938,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -68966,7 +68964,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -68992,7 +68990,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -69018,7 +69016,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -69044,7 +69042,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -69070,7 +69068,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -69096,7 +69094,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -69122,7 +69120,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -69148,7 +69146,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -69174,7 +69172,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -69245,7 +69243,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -69262,7 +69260,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -69279,7 +69277,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -69296,7 +69294,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -69313,7 +69311,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -69330,7 +69328,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -69347,7 +69345,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -69364,7 +69362,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -69381,7 +69379,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -69398,7 +69396,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -69415,7 +69413,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -69432,7 +69430,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -69449,7 +69447,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -69466,7 +69464,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -69483,7 +69481,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -69500,7 +69498,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -69517,7 +69515,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -69534,7 +69532,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -69551,7 +69549,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -69568,7 +69566,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -69585,7 +69583,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -69602,7 +69600,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -69619,7 +69617,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -69636,7 +69634,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -69653,7 +69651,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -69670,7 +69668,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -69687,7 +69685,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -69704,7 +69702,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -69721,7 +69719,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -69738,7 +69736,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -69755,7 +69753,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -69772,7 +69770,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -69789,7 +69787,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -69806,7 +69804,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -69823,7 +69821,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -69840,7 +69838,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -69857,7 +69855,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -69874,7 +69872,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -69891,7 +69889,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -69908,7 +69906,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -69925,7 +69923,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -69942,7 +69940,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -69959,7 +69957,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -69976,7 +69974,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -69993,7 +69991,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -70010,7 +70008,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -70027,7 +70025,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -70044,7 +70042,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -70061,7 +70059,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -70078,7 +70076,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -70095,7 +70093,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -70112,7 +70110,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -70129,7 +70127,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -70146,7 +70144,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -70163,7 +70161,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -70180,7 +70178,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -70197,7 +70195,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -70214,7 +70212,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -70231,7 +70229,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -70248,7 +70246,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -70265,7 +70263,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -70282,7 +70280,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -70299,7 +70297,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -70316,7 +70314,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -70333,7 +70331,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -70350,7 +70348,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -70367,7 +70365,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -70384,7 +70382,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -167,6 +167,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Paraguay power generation by type (ANDE / Itaipu / Yacyreta) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -470,6 +471,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Paraguay hydro: domestic use vs exports (to Aug/26)</a:t>
             </a:r>
           </a:p>

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -31,8 +31,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -72,13 +72,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -168,7 +167,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Paraguay power generation by type (ANDE / Itaipu / Yacyreta) (to Aug/26)</a:t>
+              <a:t>Paraguay power generation by type (ANDE / Itaipu / Yacyreta) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -198,12 +197,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +225,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -254,12 +253,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -282,12 +281,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -310,12 +309,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$69</f>
+              <f>'Chart'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -338,12 +337,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$69</f>
+              <f>'Chart'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -366,12 +365,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$69</f>
+              <f>'Chart'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -472,7 +471,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Paraguay hydro: domestic use vs exports (to Aug/26)</a:t>
+              <a:t>Paraguay hydro: domestic use vs exports (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -502,12 +501,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$A$2:$A$69</f>
+              <f>'Chart - Domestic vs exports'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$B$2:$B$69</f>
+              <f>'Chart - Domestic vs exports'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -530,12 +529,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$A$2:$A$69</f>
+              <f>'Chart - Domestic vs exports'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$C$2:$C$69</f>
+              <f>'Chart - Domestic vs exports'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -558,12 +557,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$A$2:$A$69</f>
+              <f>'Chart - Domestic vs exports'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$D$2:$D$69</f>
+              <f>'Chart - Domestic vs exports'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -600,12 +599,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$A$2:$A$69</f>
+              <f>'Chart - Domestic vs exports'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Domestic vs exports'!$E$2:$E$69</f>
+              <f>'Chart - Domestic vs exports'!$E$2:$E$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1083,6 +1082,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1097,6 +1097,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1111,6 +1112,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1136,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2101"/>
+  <dimension ref="A1:D2126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30559,6 +30561,356 @@
       </c>
       <c r="D2101" t="n">
         <v>197978</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>117793.2</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>65678.7</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>183471.9</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>107164.7</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>52727.3</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>159892</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>95497</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>59995.3</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>155492.4</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>126408.7</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>64533.7</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>190942.4</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>134090</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>58737.4</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>192827.4</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>137305</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>60307.5</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>197612.6</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>124370.2</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>57634.8</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>182005</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>137654.8</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>56887.9</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>194542.6</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>116311.5</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>52911.1</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>169222.6</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>102040.6</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>53105.4</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>155146</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>104269.9</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>46487.6</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>150757.5</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>109207.8</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>47566</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>156773.8</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>127506.2</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>44547.3</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>172053.5</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>126013.4</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>43130.2</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>169143.7</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>126210.7</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>45937.3</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>172148</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>113280.6</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>47603</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>160883.6</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>92923.10000000001</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>38862.4</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>131785.6</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>109947.4</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>39959.1</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>149906.4</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>113816.6</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>34460.9</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>148277.5</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>113870.8</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>35692.6</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>149563.4</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>114820.2</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>36566.9</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>151387</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>118246.2</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>37856.6</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>156102.8</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>108654.3</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>36941</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>145595.3</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>91729</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>44876.5</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>136605.4</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>121774.5</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>45902.8</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>167677.3</v>
       </c>
     </row>
   </sheetData>
@@ -31506,7 +31858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31535,6 +31887,17 @@
       </c>
       <c r="C2" s="4" t="n">
         <v>46297</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1836432</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>46322</v>
       </c>
     </row>
   </sheetData>
@@ -31548,7 +31911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2101"/>
+  <dimension ref="A1:E2126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67275,6 +67638,431 @@
         <v>364.2</v>
       </c>
       <c r="E2101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>55776</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>5490.7</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>58072.7</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>6897.8</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>62591.2</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>2304.1</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>293.7</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>61845</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>3026.9</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>59119.4</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>5205.3</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>286</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>51714.6</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>12231.8</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>282.1</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>51942.3</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>10085.1</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>59433.7</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>4389.4</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>298.8</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>60775.8</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>2933.7</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>60657.3</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>2892.5</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>60169.6</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>2781.4</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>57719.8</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>3402.6</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>280.4</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>56094.6</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>3866.1</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>284.7</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>53692.9</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>3870.8</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>53229.1</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>4470</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>54816.7</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>2375.5</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>57297.3</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>2100.1</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>55412.7</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>3922.8</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>53462</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>4986.6</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>49678.3</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>9558.4</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>54851.2</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>5288.3</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>46399.5</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>14000.9</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>50620.5</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>9942.6</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>56920.2</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>2951.9</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>56472.5</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>3084.1</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -67383,7 +68171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -67432,7 +68220,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -67458,7 +68246,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -67484,7 +68272,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -67510,7 +68298,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -67536,7 +68324,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -67562,7 +68350,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -67588,7 +68376,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -67614,7 +68402,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -67640,7 +68428,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -67666,7 +68454,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -67692,7 +68480,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -67718,7 +68506,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -67744,7 +68532,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -67770,7 +68558,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -67796,7 +68584,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -67822,7 +68610,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -67848,7 +68636,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -67874,7 +68662,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -67900,7 +68688,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -67926,7 +68714,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -67952,7 +68740,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -67978,7 +68766,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -68004,7 +68792,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -68030,7 +68818,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -68056,7 +68844,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -68082,7 +68870,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -68108,7 +68896,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -68134,7 +68922,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -68160,7 +68948,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -68186,7 +68974,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -68212,7 +69000,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -68238,7 +69026,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -68264,7 +69052,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -68290,7 +69078,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -68316,7 +69104,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -68342,7 +69130,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -68368,7 +69156,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -68394,7 +69182,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -68420,7 +69208,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -68446,7 +69234,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -68472,7 +69260,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -68498,7 +69286,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -68524,7 +69312,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -68550,7 +69338,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -68576,7 +69364,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -68602,7 +69390,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -68628,7 +69416,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -68654,7 +69442,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -68680,7 +69468,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -68706,7 +69494,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -68732,7 +69520,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -68758,7 +69546,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -68784,7 +69572,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -68810,7 +69598,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -68836,7 +69624,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -68862,7 +69650,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -68888,7 +69676,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -68914,7 +69702,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -68940,7 +69728,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -68966,7 +69754,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -68992,7 +69780,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -69018,7 +69806,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -69044,7 +69832,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -69070,7 +69858,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -69096,7 +69884,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -69122,7 +69910,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -69148,7 +69936,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -69174,7 +69962,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -69196,6 +69984,32 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4530.7203</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69211,7 +70025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -69245,7 +70059,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -69262,7 +70076,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -69279,7 +70093,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -69296,7 +70110,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -69313,7 +70127,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -69330,7 +70144,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -69347,7 +70161,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -69364,7 +70178,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -69381,7 +70195,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -69398,7 +70212,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -69415,7 +70229,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -69432,7 +70246,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -69449,7 +70263,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -69466,7 +70280,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -69483,7 +70297,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -69500,7 +70314,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -69517,7 +70331,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -69534,7 +70348,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -69551,7 +70365,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -69568,7 +70382,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -69585,7 +70399,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -69602,7 +70416,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -69619,7 +70433,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -69636,7 +70450,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -69653,7 +70467,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -69670,7 +70484,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -69687,7 +70501,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -69704,7 +70518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -69721,7 +70535,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -69738,7 +70552,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -69755,7 +70569,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -69772,7 +70586,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -69789,7 +70603,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -69806,7 +70620,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -69823,7 +70637,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -69840,7 +70654,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -69857,7 +70671,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -69874,7 +70688,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -69891,7 +70705,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -69908,7 +70722,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -69925,7 +70739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -69942,7 +70756,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -69959,7 +70773,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -69976,7 +70790,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -69993,7 +70807,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -70010,7 +70824,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -70027,7 +70841,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -70044,7 +70858,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -70061,7 +70875,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -70078,7 +70892,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -70095,7 +70909,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -70112,7 +70926,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -70129,7 +70943,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -70146,7 +70960,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -70163,7 +70977,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -70180,7 +70994,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -70197,7 +71011,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -70214,7 +71028,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -70231,7 +71045,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -70248,7 +71062,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -70265,7 +71079,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -70282,7 +71096,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -70299,7 +71113,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -70316,7 +71130,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -70333,7 +71147,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -70350,7 +71164,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -70367,7 +71181,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -70384,7 +71198,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -70398,6 +71212,23 @@
       </c>
       <c r="E69" t="n">
         <v>4225</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2553.8</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1237.4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>706.4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4530.7</v>
       </c>
     </row>
   </sheetData>
@@ -70412,7 +71243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72850,6 +73681,41 @@
       </c>
       <c r="K69" t="n">
         <v>4224985.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4530720.3</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4530720.3</v>
       </c>
     </row>
   </sheetData>
@@ -75932,8 +76798,19 @@
       <c r="A70" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="B70" t="n">
+        <v>2342000</v>
+      </c>
       <c r="C70" t="n">
         <v>4816732.1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7225000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Itaipu monthly report</t>
+        </is>
       </c>
       <c r="F70" t="n">
         <v>1624650.4</v>
@@ -75953,6 +76830,9 @@
       </c>
       <c r="J70" t="n">
         <v>211790.2</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1836432</v>
       </c>
       <c r="L70" t="n">
         <v>1836440.6</v>
@@ -75972,7 +76852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77364,6 +78244,26 @@
         <v>4225</v>
       </c>
       <c r="F69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1237.4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>706.4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2553.8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4530.7</v>
+      </c>
+      <c r="F70" t="b">
         <v>0</v>
       </c>
     </row>
@@ -77378,7 +78278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78144,6 +79044,17 @@
       </c>
       <c r="C69" t="n">
         <v>2547144.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2545294.8</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2545294.8</v>
       </c>
     </row>
   </sheetData>
@@ -78427,19 +79338,19 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>31.15</v>
+        <v>35.68</v>
       </c>
       <c r="D7" t="n">
-        <v>21.6</v>
+        <v>24.15</v>
       </c>
       <c r="E7" t="n">
-        <v>6.12</v>
+        <v>7.35</v>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.96</v>
       </c>
     </row>
   </sheetData>
@@ -78453,7 +79364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80355,6 +81266,34 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B71" t="n">
+        <v>21619</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2342</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7225</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3693</v>
+      </c>
+      <c r="F71" t="n">
+        <v>58370</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.itaipu.gov.py/noticias/energia/itaipu-suministro-21-619-gwh-de-energia-electrica-a-la-ande-de-enero-a-setiembre-de-2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2126"/>
+  <dimension ref="A1:D2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30911,6 +30911,20 @@
       </c>
       <c r="D2126" t="n">
         <v>167677.3</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>118934.7</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>40806.7</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>159741.3</v>
       </c>
     </row>
   </sheetData>
@@ -31897,7 +31911,7 @@
         <v>1836432</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2127"/>
+  <dimension ref="A1:D2128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30925,6 +30925,20 @@
       </c>
       <c r="D2127" t="n">
         <v>159741.3</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B2128" t="n">
+        <v>121555.2</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>41575.1</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>163130.2</v>
       </c>
     </row>
   </sheetData>
@@ -31911,7 +31925,7 @@
         <v>1836432</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
   </sheetData>
@@ -31925,7 +31939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2126"/>
+  <dimension ref="A1:E2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68077,6 +68091,23 @@
         <v>0</v>
       </c>
       <c r="E2126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>53951.5</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>4421.7</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2127" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2128"/>
+  <dimension ref="A1:D2129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30939,6 +30939,20 @@
       </c>
       <c r="D2128" t="n">
         <v>163130.2</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>128502.5</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>45499.4</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>174001.9</v>
       </c>
     </row>
   </sheetData>
@@ -31925,7 +31939,7 @@
         <v>1836432</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
   </sheetData>
@@ -31939,7 +31953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2127"/>
+  <dimension ref="A1:E2128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68108,6 +68122,23 @@
         <v>0</v>
       </c>
       <c r="E2127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B2128" t="n">
+        <v>52828.2</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>7322.8</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2128" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/paraguay_power_generation_daily.xlsx
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2129"/>
+  <dimension ref="A1:D2130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30953,6 +30953,20 @@
       </c>
       <c r="D2129" t="n">
         <v>174001.9</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B2130" t="n">
+        <v>130171.5</v>
+      </c>
+      <c r="C2130" t="n">
+        <v>39262.3</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>169433.8</v>
       </c>
     </row>
   </sheetData>
@@ -31939,7 +31953,7 @@
         <v>1836432</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
   </sheetData>
@@ -31953,7 +31967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2128"/>
+  <dimension ref="A1:E2129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68139,6 +68153,23 @@
         <v>0</v>
       </c>
       <c r="E2128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>55221.8</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>4925.3</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2129" t="n">
         <v>0</v>
       </c>
     </row>
